--- a/Bin/RejectedMaterial.xlsx
+++ b/Bin/RejectedMaterial.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ERP SOURCE CODE\Bin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lys_erp\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F25748-8792-43A9-91E8-245D44F6BC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,7 +103,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -167,6 +168,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -175,9 +179,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -197,9 +198,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -237,9 +238,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -274,7 +275,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -309,7 +310,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -482,7 +483,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -503,19 +504,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="72.75" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:11" ht="78.75" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -566,103 +567,103 @@
       <c r="K3" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="33" customHeight="1">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="6" t="s">
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="K5" s="7"/>
+      <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -676,13 +677,19 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A5:D5"/>
   </mergeCells>
-  <pageMargins left="0.14000000000000001" right="0.14000000000000001" top="0.19" bottom="0" header="0.19685039370078741" footer="0.19"/>
+  <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.19685039370078741" bottom="0" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="77" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter xml:space="preserve">&amp;R
+A-QIP-019A
+QIP/VII/59/01
+</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
@@ -691,7 +698,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
